--- a/data/gravel/Vielo V+1 2025.xlsx
+++ b/data/gravel/Vielo V+1 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5397C0C-C2E0-9645-90B8-7E2C25BB4F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8935E66-62F9-484A-A05E-F44B0307F212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3400" yWindow="620" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>press fit</t>
+  </si>
+  <si>
+    <t>frame size</t>
   </si>
 </sst>
 </file>
@@ -823,22 +826,24 @@
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
